--- a/output/keychal_output.xlsx
+++ b/output/keychal_output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,30 +473,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e16</t>
+          <t>69829406eb123e27b6749e35</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>혈압낮추는법</t>
+          <t>간기능영양제</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>모모둥이</t>
+          <t>셀럽주부</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>3970</v>
+        <v>1272</v>
       </c>
       <c r="F2" t="n">
-        <v>3430</v>
+        <v>160</v>
       </c>
       <c r="G2" t="n">
-        <v>46700</v>
+        <v>1350</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -507,30 +507,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e17</t>
+          <t>69829406eb123e27b6749e55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>갱년기영양제</t>
+          <t>간기능개선제</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>모모둥이</t>
+          <t>수미지</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>6987</v>
+        <v>5699</v>
       </c>
       <c r="F3" t="n">
-        <v>3880</v>
+        <v>180</v>
       </c>
       <c r="G3" t="n">
-        <v>26900</v>
+        <v>1130</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -541,30 +541,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e18</t>
+          <t>69829406eb123e27b6749e57</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>여성갱년기증상</t>
+          <t>간보호제</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>모모둥이</t>
+          <t>수미지</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>7398</v>
+        <v>9425</v>
       </c>
       <c r="F4" t="n">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="G4" t="n">
-        <v>1330</v>
+        <v>980</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -575,30 +575,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e19</t>
+          <t>69829406eb123e27b6749e27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>흑염소진액효능</t>
+          <t>유아영양제</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>모모둥이</t>
+          <t>봉봉댁</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>3744</v>
+        <v>7532</v>
       </c>
       <c r="F5" t="n">
-        <v>810</v>
+        <v>180</v>
       </c>
       <c r="G5" t="n">
-        <v>8050</v>
+        <v>1130</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -609,30 +609,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e1a</t>
+          <t>69829406eb123e27b6749e28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>흑염소즙효능</t>
+          <t>유아비타민</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>모모둥이</t>
+          <t>봉봉댁</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>6394</v>
+        <v>8321</v>
       </c>
       <c r="F6" t="n">
-        <v>270</v>
+        <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>2160</v>
+        <v>780</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -643,30 +643,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e1b</t>
+          <t>69829406eb123e27b6749e2a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>염소즙효능</t>
+          <t>울금효능</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>모모둥이</t>
+          <t>셀럽주부</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>6335.6875</v>
+        <v>3119</v>
       </c>
       <c r="F7" t="n">
-        <v>160</v>
+        <v>390</v>
       </c>
       <c r="G7" t="n">
-        <v>1890</v>
+        <v>7390</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -677,30 +677,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e1c</t>
+          <t>69829406eb123e27b6749e2c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>아기성장발달</t>
+          <t>몸속염증제거</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>모모둥이</t>
+          <t>셀럽주부</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>3030</v>
+        <v>7112</v>
       </c>
       <c r="F8" t="n">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="G8" t="n">
-        <v>2140</v>
+        <v>730</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -711,216 +711,216 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e1d</t>
+          <t>69829406eb123e27b6749e2d</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>아기기는시기</t>
+          <t>만성염증증상</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>모모둥이</t>
+          <t>셀럽주부</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>700.984375</v>
+        <v>121</v>
       </c>
       <c r="F9" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="G9" t="n">
-        <v>3090</v>
+        <v>840</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>낮음</t>
+          <t>높음</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e1e</t>
+          <t>69829406eb123e27b6749e38</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>배밀이시기</t>
+          <t>남자갱년기증상</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>모모둥이</t>
+          <t>셀럽주부</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>3102</v>
+        <v>3736</v>
       </c>
       <c r="F10" t="n">
-        <v>150</v>
+        <v>880</v>
       </c>
       <c r="G10" t="n">
-        <v>5640</v>
+        <v>7960</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>중간</t>
+          <t>높음</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e1f</t>
+          <t>69829406eb123e27b6749e46</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>아기배밀이시기</t>
+          <t>커큐민효능</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>모모둥이</t>
+          <t>소신있는라이프</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>3419</v>
+        <v>2248</v>
       </c>
       <c r="F11" t="n">
-        <v>50</v>
+        <v>3160</v>
       </c>
       <c r="G11" t="n">
-        <v>1070</v>
+        <v>32100</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>중간</t>
+          <t>높음</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e20</t>
+          <t>69829406eb123e27b6749e47</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>아기이나는시기</t>
+          <t>강황의효능</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>모모둥이</t>
+          <t>소신있는라이프</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>1525.65625</v>
+        <v>3866</v>
       </c>
       <c r="F12" t="n">
-        <v>190</v>
+        <v>720</v>
       </c>
       <c r="G12" t="n">
-        <v>5350</v>
+        <v>18600</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>중간</t>
+          <t>높음</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e21</t>
+          <t>69829406eb123e27b6749e49</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>아기이나는순서</t>
+          <t>신경성위염</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>모모둥이</t>
+          <t>푸들ol</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>780</v>
+        <v>6487</v>
       </c>
       <c r="F13" t="n">
-        <v>180</v>
+        <v>290</v>
       </c>
       <c r="G13" t="n">
-        <v>4780</v>
+        <v>1800</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>중간</t>
+          <t>높음</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e22</t>
+          <t>69829406eb123e27b6749e4b</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>당뇨정상수치</t>
+          <t>염증약</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>모모둥이</t>
+          <t>푸들ol</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>7096</v>
+        <v>5954.34375</v>
       </c>
       <c r="F14" t="n">
-        <v>2140</v>
+        <v>400</v>
       </c>
       <c r="G14" t="n">
-        <v>31400</v>
+        <v>4060</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e23</t>
+          <t>69829406eb123e27b6749e1c</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>혈당관리</t>
+          <t>아기성장발달</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>6691</v>
+        <v>2292</v>
       </c>
       <c r="F15" t="n">
-        <v>1250</v>
+        <v>210</v>
       </c>
       <c r="G15" t="n">
-        <v>5200</v>
+        <v>1960</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -949,98 +949,98 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e24</t>
+          <t>69829406eb123e27b6749e1d</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>고혈압증상</t>
+          <t>아기기는시기</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>푸들ol</t>
+          <t>모모둥이</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4322</v>
+        <v>780</v>
       </c>
       <c r="F16" t="n">
-        <v>2990</v>
+        <v>130</v>
       </c>
       <c r="G16" t="n">
-        <v>30700</v>
+        <v>3270</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e25</t>
+          <t>69829406eb123e27b6749e20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>돌선물</t>
+          <t>아기이나는시기</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>봉봉댁</t>
+          <t>모모둥이</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>8817</v>
+        <v>729</v>
       </c>
       <c r="F17" t="n">
-        <v>2490</v>
+        <v>180</v>
       </c>
       <c r="G17" t="n">
-        <v>15800</v>
+        <v>5890</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e26</t>
+          <t>69829406eb123e27b6749e32</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>돌선물추천</t>
+          <t>산후풍치료</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>봉봉댁</t>
+          <t>셀럽주부</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>5318</v>
+        <v>6341.65625</v>
       </c>
       <c r="F18" t="n">
-        <v>660</v>
+        <v>40</v>
       </c>
       <c r="G18" t="n">
-        <v>6040</v>
+        <v>370</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1051,30 +1051,30 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e27</t>
+          <t>69829406eb123e27b6749e33</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>유아영양제</t>
+          <t>간기능</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>봉봉댁</t>
+          <t>셀럽주부</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>6713</v>
+        <v>6779</v>
       </c>
       <c r="F19" t="n">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="G19" t="n">
-        <v>1240</v>
+        <v>1060</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1085,30 +1085,30 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e28</t>
+          <t>69829406eb123e27b6749e17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>유아비타민</t>
+          <t>갱년기영양제</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>봉봉댁</t>
+          <t>모모둥이</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>6730</v>
+        <v>6969.6875</v>
       </c>
       <c r="F20" t="n">
-        <v>120</v>
+        <v>3330</v>
       </c>
       <c r="G20" t="n">
-        <v>870</v>
+        <v>26500</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1119,30 +1119,30 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e29</t>
+          <t>69829406eb123e27b6749e1b</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>유아오메가3</t>
+          <t>염소즙효능</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>봉봉댁</t>
+          <t>모모둥이</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>4876</v>
+        <v>6131.6875</v>
       </c>
       <c r="F21" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="G21" t="n">
-        <v>2590</v>
+        <v>1860</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1153,64 +1153,64 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e2a</t>
+          <t>69829406eb123e27b6749e1e</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>울금효능</t>
+          <t>배밀이시기</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>셀럽주부</t>
+          <t>모모둥이</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>6785.6875</v>
+        <v>4528</v>
       </c>
       <c r="F22" t="n">
-        <v>450</v>
+        <v>120</v>
       </c>
       <c r="G22" t="n">
-        <v>7590</v>
+        <v>5470</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e2b</t>
+          <t>69829406eb123e27b6749e24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>울금강황</t>
+          <t>고혈압증상</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>셀럽주부</t>
+          <t>푸들ol</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>6955.671875</v>
+        <v>4554</v>
       </c>
       <c r="F23" t="n">
-        <v>110</v>
+        <v>2620</v>
       </c>
       <c r="G23" t="n">
-        <v>1120</v>
+        <v>29600</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1221,12 +1221,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e2c</t>
+          <t>69829406eb123e27b6749e2b</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>몸속염증제거</t>
+          <t>울금강황</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1235,16 +1235,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>6635</v>
+        <v>6691</v>
       </c>
       <c r="F24" t="n">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="G24" t="n">
-        <v>940</v>
+        <v>1110</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1255,30 +1255,30 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e2d</t>
+          <t>69829406eb123e27b6749e52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>만성염증증상</t>
+          <t>골감소증</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>셀럽주부</t>
+          <t>갬성주부</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>121</v>
+        <v>10030</v>
       </c>
       <c r="F25" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G25" t="n">
-        <v>740</v>
+        <v>2230</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1289,30 +1289,30 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e2e</t>
+          <t>69829406eb123e27b6749e19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>만성편도염</t>
+          <t>흑염소진액효능</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>셀럽주부</t>
+          <t>모모둥이</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>5229</v>
+        <v>3678</v>
       </c>
       <c r="F26" t="n">
-        <v>120</v>
+        <v>780</v>
       </c>
       <c r="G26" t="n">
-        <v>650</v>
+        <v>8860</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1323,64 +1323,64 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e2f</t>
+          <t>69829406eb123e27b6749e1f</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>혈당조절</t>
+          <t>아기배밀이시기</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>셀럽주부</t>
+          <t>모모둥이</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>9388</v>
+        <v>3432</v>
       </c>
       <c r="F27" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="G27" t="n">
-        <v>990</v>
+        <v>1120</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e30</t>
+          <t>69829406eb123e27b6749e48</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>당체크</t>
+          <t>스트레스성위염</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>셀럽주부</t>
+          <t>푸들ol</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1182</v>
+        <v>4138</v>
       </c>
       <c r="F28" t="n">
-        <v>70</v>
+        <v>470</v>
       </c>
       <c r="G28" t="n">
-        <v>530</v>
+        <v>4240</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1391,30 +1391,30 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e31</t>
+          <t>69829406eb123e27b6749e56</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>산후풍증상</t>
+          <t>간기능저하</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>셀럽주부</t>
+          <t>수미지</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>6696.6875</v>
+        <v>8642</v>
       </c>
       <c r="F29" t="n">
         <v>90</v>
       </c>
       <c r="G29" t="n">
-        <v>1840</v>
+        <v>980</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1425,30 +1425,30 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e32</t>
+          <t>69829406eb123e27b6749e59</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>산후풍치료</t>
+          <t>저밀도콜레스테롤</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>셀럽주부</t>
+          <t>사남매가사는곳</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>6361.65625</v>
+        <v>10702</v>
       </c>
       <c r="F30" t="n">
-        <v>30</v>
+        <v>780</v>
       </c>
       <c r="G30" t="n">
-        <v>370</v>
+        <v>5110</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1459,30 +1459,30 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e33</t>
+          <t>69829406eb123e27b6749e5a</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>간기능</t>
+          <t>콜레스테롤낮추는방법</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>셀럽주부</t>
+          <t>사남매가사는곳</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>6614</v>
+        <v>4621</v>
       </c>
       <c r="F31" t="n">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="G31" t="n">
-        <v>1210</v>
+        <v>6570</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1493,30 +1493,30 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e34</t>
+          <t>69829406eb123e27b6749e1a</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>간회복</t>
+          <t>흑염소즙효능</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>셀럽주부</t>
+          <t>모모둥이</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>6200.015625</v>
+        <v>7014.6875</v>
       </c>
       <c r="F32" t="n">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="G32" t="n">
-        <v>580</v>
+        <v>2160</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1527,30 +1527,30 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e35</t>
+          <t>69829406eb123e27b6749e29</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>간기능영양제</t>
+          <t>유아오메가3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>셀럽주부</t>
+          <t>봉봉댁</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1272</v>
+        <v>4894</v>
       </c>
       <c r="F33" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="G33" t="n">
-        <v>1480</v>
+        <v>2200</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1561,12 +1561,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e36</t>
+          <t>69829406eb123e27b6749e30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>혈당낮추는법</t>
+          <t>당체크</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1578,13 +1578,13 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>7825</v>
+        <v>1218</v>
       </c>
       <c r="F34" t="n">
-        <v>1160</v>
+        <v>70</v>
       </c>
       <c r="G34" t="n">
-        <v>8110</v>
+        <v>510</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1595,12 +1595,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e37</t>
+          <t>69829406eb123e27b6749e39</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>혈당영양제</t>
+          <t>남성갱년기영양제</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1612,13 +1612,13 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>10303</v>
+        <v>6228.34375</v>
       </c>
       <c r="F35" t="n">
-        <v>840</v>
+        <v>230</v>
       </c>
       <c r="G35" t="n">
-        <v>3270</v>
+        <v>1460</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1629,30 +1629,30 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e38</t>
+          <t>69829406eb123e27b6749e18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>남자갱년기증상</t>
+          <t>여성갱년기증상</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>셀럽주부</t>
+          <t>모모둥이</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>5282.5</v>
+        <v>7924</v>
       </c>
       <c r="F36" t="n">
-        <v>980</v>
+        <v>220</v>
       </c>
       <c r="G36" t="n">
-        <v>7890</v>
+        <v>1480</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1663,46 +1663,46 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e39</t>
+          <t>69829406eb123e27b6749e21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>남성갱년기영양제</t>
+          <t>아기이나는순서</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>셀럽주부</t>
+          <t>모모둥이</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>6409.6875</v>
+        <v>729</v>
       </c>
       <c r="F37" t="n">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="G37" t="n">
-        <v>1260</v>
+        <v>5270</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e3a</t>
+          <t>69829406eb123e27b6749e31</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>남성갱년기증상</t>
+          <t>산후풍증상</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1711,16 +1711,16 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>7376.671875</v>
+        <v>6649.6875</v>
       </c>
       <c r="F38" t="n">
-        <v>620</v>
+        <v>80</v>
       </c>
       <c r="G38" t="n">
-        <v>4330</v>
+        <v>1850</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1731,12 +1731,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e3b</t>
+          <t>69829406eb123e27b6749e3a</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>테스토스테론</t>
+          <t>남성갱년기증상</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1745,16 +1745,16 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>7416</v>
+        <v>6086</v>
       </c>
       <c r="F39" t="n">
-        <v>2150</v>
+        <v>540</v>
       </c>
       <c r="G39" t="n">
-        <v>13100</v>
+        <v>4210</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1765,30 +1765,30 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e3c</t>
+          <t>69829406eb123e27b6749e58</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>남성호르몬</t>
+          <t>콜레스테롤낮추는음식</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>셀럽주부</t>
+          <t>사남매가사는곳</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>7320</v>
+        <v>2428</v>
       </c>
       <c r="F40" t="n">
-        <v>700</v>
+        <v>1070</v>
       </c>
       <c r="G40" t="n">
-        <v>7180</v>
+        <v>10300</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1799,30 +1799,30 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e3d</t>
+          <t>69829406eb123e27b6749e16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>무릎통증</t>
+          <t>혈압낮추는법</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>셀럽주부</t>
+          <t>모모둥이</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>8432</v>
+        <v>4100</v>
       </c>
       <c r="F41" t="n">
-        <v>3790</v>
+        <v>2830</v>
       </c>
       <c r="G41" t="n">
-        <v>26300</v>
+        <v>43100</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1833,12 +1833,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e3e</t>
+          <t>69829406eb123e27b6749e2e</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>무릎염증</t>
+          <t>만성편도염</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1850,13 +1850,13 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>9140</v>
+        <v>4769</v>
       </c>
       <c r="F42" t="n">
-        <v>560</v>
+        <v>90</v>
       </c>
       <c r="G42" t="n">
-        <v>4880</v>
+        <v>630</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1867,12 +1867,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e3f</t>
+          <t>69829406eb123e27b6749e2f</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>무릎소리</t>
+          <t>혈당조절</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1881,16 +1881,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>5605.328125</v>
+        <v>9595</v>
       </c>
       <c r="F43" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="G43" t="n">
-        <v>1290</v>
+        <v>840</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1901,12 +1901,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e40</t>
+          <t>69829406eb123e27b6749e34</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>간영양제</t>
+          <t>간회복</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1918,13 +1918,13 @@
         <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>10793</v>
+        <v>6076.015625</v>
       </c>
       <c r="F44" t="n">
-        <v>3090</v>
+        <v>80</v>
       </c>
       <c r="G44" t="n">
-        <v>20300</v>
+        <v>500</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1935,30 +1935,30 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e41</t>
+          <t>69829406eb123e27b6749e4a</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>밀크씨슬효능</t>
+          <t>염증주사</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>셀럽주부</t>
+          <t>푸들ol</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1345</v>
+        <v>6196.6875</v>
       </c>
       <c r="F45" t="n">
-        <v>1510</v>
+        <v>780</v>
       </c>
       <c r="G45" t="n">
-        <v>11500</v>
+        <v>5520</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1969,848 +1969,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>69829406eb123e27b6749e42</t>
+          <t>69829406eb123e27b6749e51</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>간건강</t>
+          <t>골다공증에좋은음식</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>셀럽주부</t>
+          <t>갬성주부</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>8617</v>
+        <v>4813</v>
       </c>
       <c r="F46" t="n">
-        <v>280</v>
+        <v>540</v>
       </c>
       <c r="G46" t="n">
-        <v>1360</v>
+        <v>7280</v>
       </c>
       <c r="H46" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e43</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>간영양제추천</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>셀럽주부</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" t="n">
-        <v>10022</v>
-      </c>
-      <c r="F47" t="n">
-        <v>400</v>
-      </c>
-      <c r="G47" t="n">
-        <v>2920</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e44</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>산후보약</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>셀럽주부</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" t="n">
-        <v>6646.6875</v>
-      </c>
-      <c r="F48" t="n">
-        <v>350</v>
-      </c>
-      <c r="G48" t="n">
-        <v>2260</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e45</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>산후조리</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>셀럽주부</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" t="n">
-        <v>8146.34375</v>
-      </c>
-      <c r="F49" t="n">
-        <v>220</v>
-      </c>
-      <c r="G49" t="n">
-        <v>1070</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e46</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>커큐민효능</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>소신있는라이프</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="n">
-        <v>2248</v>
-      </c>
-      <c r="F50" t="n">
-        <v>3680</v>
-      </c>
-      <c r="G50" t="n">
-        <v>33500</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e47</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>강황의효능</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>소신있는라이프</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>3</v>
-      </c>
-      <c r="E51" t="n">
-        <v>6132</v>
-      </c>
-      <c r="F51" t="n">
-        <v>880</v>
-      </c>
-      <c r="G51" t="n">
-        <v>20200</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e48</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>스트레스성위염</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>푸들ol</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>2</v>
-      </c>
-      <c r="E52" t="n">
-        <v>6130</v>
-      </c>
-      <c r="F52" t="n">
-        <v>510</v>
-      </c>
-      <c r="G52" t="n">
-        <v>4600</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e49</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>신경성위염</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>푸들ol</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" t="n">
-        <v>6551</v>
-      </c>
-      <c r="F53" t="n">
-        <v>330</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1820</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e4a</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>염증주사</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>푸들ol</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>2</v>
-      </c>
-      <c r="E54" t="n">
-        <v>6102.6875</v>
-      </c>
-      <c r="F54" t="n">
-        <v>910</v>
-      </c>
-      <c r="G54" t="n">
-        <v>6260</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e4b</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>염증약</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>푸들ol</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" t="n">
-        <v>5465.34375</v>
-      </c>
-      <c r="F55" t="n">
-        <v>480</v>
-      </c>
-      <c r="G55" t="n">
-        <v>4290</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e4c</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>항산화영양제</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>푸들ol</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>2</v>
-      </c>
-      <c r="E56" t="n">
-        <v>9472</v>
-      </c>
-      <c r="F56" t="n">
-        <v>720</v>
-      </c>
-      <c r="G56" t="n">
-        <v>4360</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e4d</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>항산화식품</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>푸들ol</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" t="n">
-        <v>6958.6875</v>
-      </c>
-      <c r="F57" t="n">
-        <v>100</v>
-      </c>
-      <c r="G57" t="n">
-        <v>810</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e4e</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>어지러움증상</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>푸들ol</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" t="n">
-        <v>8931</v>
-      </c>
-      <c r="F58" t="n">
-        <v>780</v>
-      </c>
-      <c r="G58" t="n">
-        <v>11200</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e4f</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>어지러움약</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>푸들ol</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>2</v>
-      </c>
-      <c r="E59" t="n">
-        <v>6800.6875</v>
-      </c>
-      <c r="F59" t="n">
-        <v>140</v>
-      </c>
-      <c r="G59" t="n">
-        <v>990</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e50</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>염증수치</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>류애</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="n">
-        <v>6766</v>
-      </c>
-      <c r="F60" t="n">
-        <v>1250</v>
-      </c>
-      <c r="G60" t="n">
-        <v>9680</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e51</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>골다공증에좋은음식</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>갬성주부</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="n">
-        <v>1332</v>
-      </c>
-      <c r="F61" t="n">
-        <v>640</v>
-      </c>
-      <c r="G61" t="n">
-        <v>8230</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e52</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>골감소증</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>갬성주부</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" t="n">
-        <v>11028</v>
-      </c>
-      <c r="F62" t="n">
-        <v>560</v>
-      </c>
-      <c r="G62" t="n">
-        <v>2640</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e53</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>에스트로겐영양제</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>갬성주부</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="n">
-        <v>9120</v>
-      </c>
-      <c r="F63" t="n">
-        <v>650</v>
-      </c>
-      <c r="G63" t="n">
-        <v>6560</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e54</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>폐경증상</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>갬성주부</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="n">
-        <v>8556</v>
-      </c>
-      <c r="F64" t="n">
-        <v>320</v>
-      </c>
-      <c r="G64" t="n">
-        <v>4150</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e55</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>간기능개선제</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>수미지</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" t="n">
-        <v>4577</v>
-      </c>
-      <c r="F65" t="n">
-        <v>190</v>
-      </c>
-      <c r="G65" t="n">
-        <v>1190</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e56</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>간기능저하</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>수미지</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>3</v>
-      </c>
-      <c r="E66" t="n">
-        <v>9042</v>
-      </c>
-      <c r="F66" t="n">
-        <v>120</v>
-      </c>
-      <c r="G66" t="n">
-        <v>1010</v>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e57</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>간보호제</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>수미지</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" t="n">
-        <v>9455</v>
-      </c>
-      <c r="F67" t="n">
-        <v>160</v>
-      </c>
-      <c r="G67" t="n">
-        <v>1060</v>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e58</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>콜레스테롤낮추는음식</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>사남매가사는곳</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="n">
-        <v>2378</v>
-      </c>
-      <c r="F68" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G68" t="n">
-        <v>12300</v>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e59</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>저밀도콜레스테롤</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>사남매가사는곳</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" t="n">
-        <v>7541</v>
-      </c>
-      <c r="F69" t="n">
-        <v>1130</v>
-      </c>
-      <c r="G69" t="n">
-        <v>6710</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>69829406eb123e27b6749e5a</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>콜레스테롤낮추는방법</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>사남매가사는곳</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="n">
-        <v>4297</v>
-      </c>
-      <c r="F70" t="n">
-        <v>1250</v>
-      </c>
-      <c r="G70" t="n">
-        <v>7670</v>
-      </c>
-      <c r="H70" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
